--- a/diseases/d242/2015-2019.xlsx
+++ b/diseases/d242/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.03739904245361654</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.07479808490723308</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.0560985636804248</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01869952122680827</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.09349760613404134</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0560985636804248</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.09349760613404134</v>
       </c>
@@ -5120,9 +5087,6 @@
       </c>
       <c r="O24" t="n">
         <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.03739904245361654</v>

--- a/diseases/d242/2015-2019.xlsx
+++ b/diseases/d242/2015-2019.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -751,22 +751,22 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01869952122680827</v>
+        <v>0.722468378375514</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -775,12 +775,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -813,42 +813,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -910,38 +910,38 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2019-01</t>
+          <t>2015-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1047,42 +1047,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1144,22 +1144,22 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>596</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>596</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03739904245361654</v>
+        <v>0.9156994840532739</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1206,42 +1206,42 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1303,38 +1303,38 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2019-02</t>
+          <t>2016-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>596</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>596</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1440,42 +1440,42 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.700010060538463</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -1599,42 +1599,42 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1696,38 +1696,38 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2019-03</t>
+          <t>2017-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1833,42 +1833,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>694</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>694</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07479808490723308</v>
+        <v>1.059225955370491</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT8" t="n">
@@ -1992,42 +1992,42 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2089,38 +2089,38 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2019-04</t>
+          <t>2018-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>694</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>694</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2226,42 +2226,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2323,22 +2323,22 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>721</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0560985636804248</v>
+        <v>1.096920636453131</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2347,12 +2347,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT10" t="n">
@@ -2385,42 +2385,42 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2482,38 +2482,38 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2019-05</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>721</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>721</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Lymfogranuloma venerum (LGV)</t>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2573,17 +2573,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_910_MONTHLY</t>
+          <t>SER_FR_ECDC_LGV_ANNUAL</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -2619,42 +2619,42 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -2716,22 +2716,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.01869952122680827</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2875,19 +2875,19 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2019-06</t>
+          <t>2019-01</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3109,22 +3109,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01869952122680827</v>
+        <v>0.03739904245361654</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3268,19 +3268,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2019-07</t>
+          <t>2019-02</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3502,22 +3502,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01869952122680827</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3661,19 +3661,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-03</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3895,22 +3895,22 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.09349760613404134</v>
+        <v>0.07479808490723308</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -4054,19 +4054,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2019-09-01</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-04</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2019-10</t>
+          <t>2019-05</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.09349760613404134</v>
+        <v>0</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4840,19 +4840,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-06</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5074,22 +5074,22 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0.03739904245361654</v>
+        <v>0.01869952122680827</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5233,19 +5233,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-07</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5404,6 +5404,1971 @@
         </is>
       </c>
       <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.01869952122680827</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.09349760613404134</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2019-09-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0560985636804248</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2019-10-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.09349760613404134</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2019-11-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.03739904245361654</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Lymfogranuloma venerum (LGV)</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; Kept distinct from general genital chlamydia code 904 to prevent double counting.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -5454,7 +7419,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2015-01-01</t>
         </is>
       </c>
     </row>
@@ -5525,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -5535,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -5555,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -5565,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5587,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="16">
